--- a/Tests/excel/module01_test_cases.xlsx
+++ b/Tests/excel/module01_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module01" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module01'!$A$1:$N$40</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module01_test_cases.xlsx
+++ b/Tests/excel/module01_test_cases.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module01" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module01'!$A$1:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module01'!$A$1:$N$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
+      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -73,12 +73,6 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -145,8 +139,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,8 +169,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -254,25 +248,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -291,7 +285,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,16 +303,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -398,14 +392,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +423,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +450,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +477,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +509,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +536,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +563,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +578,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1009,15 +1003,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A9, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A9, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A9, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1031,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A10, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A10, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A10, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1065,15 +1059,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A11, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A11, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A11, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1093,15 +1087,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A12, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A12, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A12, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1121,15 +1115,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A13, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A13, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A13, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1149,15 +1143,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A14, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A14, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A14, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1177,15 +1171,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A15, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A15, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A15, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1205,15 +1199,15 @@
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A16, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A16, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A16, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1233,15 +1227,15 @@
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A17, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A17, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A17, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1261,15 +1255,15 @@
         </is>
       </c>
       <c r="C18" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A18, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D18" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A18, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A18, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F18" s="33">
@@ -1289,15 +1283,15 @@
         </is>
       </c>
       <c r="C19" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A19, 'Module01'!$M$2:$M$40, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "High")</f>
         <v/>
       </c>
       <c r="D19" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A19, 'Module01'!$M$2:$M$40, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "Medium")</f>
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$40, A19, 'Module01'!$M$2:$M$40, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "Low")</f>
         <v/>
       </c>
       <c r="F19" s="27">
@@ -1344,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1490,10 +1484,14 @@
           <t>Batch is created successfully. Success notification appears. PNV26A is displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Batch is created successfully. Success notification appears. PNV26A is displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -1561,10 +1559,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -1632,10 +1634,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -1703,10 +1709,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -1774,10 +1784,14 @@
           <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -1845,10 +1859,14 @@
           <t>System rejects save. Error message appears indicating batch name is required. Saving is blocked.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>System rejects save. Error message appears indicating batch name is required. Saving is blocked.</t>
+        </is>
+      </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -1916,10 +1934,14 @@
           <t>System rejects creation. Error message appears: "A batch named "PNV26A" already exists."</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "A batch named "PNV26A" already exists."</t>
+        </is>
+      </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -1987,10 +2009,14 @@
           <t>Batch is renamed successfully. Success notification appears. PNV26C is displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Batch is renamed successfully. Success notification appears. PNV26C is displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -2058,10 +2084,14 @@
           <t>System rejects update. Error message appears: "A batch named "PNV26A" already exists."</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>System rejects update. Error message appears: "A batch named "PNV26A" already exists."</t>
+        </is>
+      </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -2129,10 +2159,14 @@
           <t>System rejects update. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>System rejects update. Error message appears: "Invalid batch name. Use format PNVyyX (e.g., PNV26A)."</t>
+        </is>
+      </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -2199,10 +2233,14 @@
           <t>Batch is archived successfully. Active status becomes false in database. The batch is hidden from active lists.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Batch is archived successfully. Active status becomes false in database. The batch is hidden from active lists.</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -2270,10 +2308,14 @@
           <t>Batch is reactivated successfully. Active status becomes true in database. The batch appears in active lists.</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Batch is reactivated successfully. Active status becomes true in database. The batch appears in active lists.</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -2340,10 +2382,14 @@
           <t>No permanent delete button is available on the interface. Archiving/status toggles are the only status-changing options.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>No permanent delete button is available on the interface. Archiving/status toggles are the only status-changing options.</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
@@ -2414,10 +2460,14 @@
           <t>Student profile is created successfully. Success notification appears. The student is active by default and displayed in the batch list.</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Student profile is created successfully. Success notification appears. The student is active by default and displayed in the batch list.</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -2486,10 +2536,14 @@
           <t>System rejects creation. Error message appears: "Duplicate student code: st001."</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>System rejects creation. Error message appears: "Duplicate student code: st001."</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -2503,7 +2557,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="120" customHeight="1">
+    <row r="17" ht="105" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M01-016</t>
@@ -2526,12 +2580,12 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Create Student with Invalid Email Format</t>
+          <t>Create Student with Missing Required Fields</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Verify that manually creating a student with an invalid email format is blocked by validation.</t>
+          <t>Verify that manually creating a student fails if required fields like student code or name are missing.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -2541,82 +2595,10 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=ST002; StudentName=Tran Thi B; Email=tranthib.st26@invalid; AssociatedBatch=PNV26A</t>
+          <t>StudentCode=; StudentName=; AssociatedBatch=PNV26A</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management and select batch PNV26A;
-2. Click Add Student;
-3. Enter ST002 and Tran Thi B;
-4. Enter email tranthib.st26@invalid;
-5. Click Save</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>System rejects saving. A validation error message requires a valid email format. Saving is blocked.</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="105" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>M01-F04</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Single Student Creation</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Create Student with Missing Required Fields</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Verify that manually creating a student fails if required fields like student code or name are missing.</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>StudentCode=; StudentName=; AssociatedBatch=PNV26A</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>1. Open Batch Management and select batch PNV26A;
 2. Click Add Student;
@@ -2624,15 +2606,93 @@
 4. Click Save</t>
         </is>
       </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Module 01</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>CSV Student Import Upsert</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Verify that bulk student import via CSV updates existing profiles and creates new profiles (Upsert behavior).</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Staff user is logged in. Student ST001 already exists; batch PNV26A exists.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>CSV row: ST001,Nguyen Van A Updated,2006-05-15,Male,nguyenvana.new@student.passerellesnumeriques.org,AssociatedBatch=PNV26A and ST003,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org,AssociatedBatch=PNV26A</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>1. Go to CSV Import page;
+2. Upload CSV containing update row for ST001 and new row for ST003;
+3. Click Import</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>System rejects saving. Validation error messages for required fields are displayed. Saving is blocked.</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
+        </is>
+      </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -2642,14 +2702,14 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Related Requirement: M01-F04, Scenario: BS-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="75" customHeight="1">
+          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>TC-M01-020</t>
+          <t>TC-M01-018</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2669,110 +2729,118 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
+          <t>CSV Student Import Rejects Duplicate Student Codes</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Verify that student bulk import via CSV rejects imports with duplicate student codes within the file.</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Staff user is logged in.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>CSV containing two rows with student code ST004</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>1. Go to CSV Import page;
+2. Upload CSV with duplicate ST004;
+3. Click Import</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>The system rejects the entire CSV file. Error message appears: "Duplicate student code: ST004.". No records are imported.</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>No duplicate student ID notification in the import file.</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Module 01</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>CSV Student Import Fails due to Missing Required Column</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Verify that student bulk import via CSV rejects files missing required columns (e.g. Student Code).</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>CSV file missing 'Student Code' header column</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>1. Open Student CSV Import page;
 2. Upload the CSV file missing Student Code;
 3. Click Import</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>The system rejects the entire CSV file. Error message appears: "Required columns must exist.". No records are imported.</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="75" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-021</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>CSV Student Import Fails due to Invalid Email Format</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Verify that bulk import via CSV rejects the file if a student email format is invalid.</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>CSV file containing a row with email 'hoangvane.st26@invalid_email_domain'</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>1. Open Student CSV Import page;
-2. Upload the CSV file containing the invalid email;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>The system rejects the import. Error message appears: "Valid email format" required. No records are updated or created.</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>No notification regarding missing student IDs in the import file.</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -2789,7 +2857,7 @@
     <row r="21" ht="120" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>TC-M01-022</t>
+          <t>TC-M01-020</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2840,10 +2908,14 @@
           <t>Student profile is updated successfully. Success notification appears. The new info is displayed immediately in lists.</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Student profile is updated successfully. Success notification appears. The new info is displayed immediately in lists.</t>
+        </is>
+      </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -2857,10 +2929,10 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="90" customHeight="1">
+    <row r="22" ht="105" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-M01-023</t>
+          <t>TC-M01-021</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2870,106 +2942,35 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>M01-F06</t>
+          <t>M01-F07</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Student Editing</t>
+          <t>Follow-up Flag</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Edit Student Code to Existing Code Blocked</t>
+          <t>Toggle Follow-up Flag Instantly</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Verify that renaming a student code to one that already exists in the system is blocked.</t>
+          <t>Verify that the follow-up flag updates immediately on the SPA interface without a page reload.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Staff user is logged in. Students ST001 and ST002 exist.</t>
+          <t>Staff user is logged in. Student ST001 is displayed in the student list.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>TargetStudent=ST002; NewStudentCode=ST001</t>
+          <t>StudentCode=ST001</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management and select student ST002;
-2. Click Edit;
-3. Change Student Code to ST001;
-4. Click Save</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>System rejects update. Error message appears: "Duplicate student code: ST001."</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F06, Scenario: BS-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-024</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>M01-F07</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Follow-up Flag</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Toggle Follow-up Flag Instantly</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Verify that the follow-up flag updates immediately on the SPA interface without a page reload.</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Student ST001 is displayed in the student list.</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>StudentCode=ST001</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>1. Navigate to student list;
 2. Locate student ST001;
@@ -2977,70 +2978,74 @@
 4. Observe the page</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>The flag status toggles instantly in the UI with no page reload. Google Sheets database updates the follow-up status immediately.</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>The "Follow-up Flag" feature for students is not yet available in this section.</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F07, Scenario: BS-07</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-025</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>M01-F08</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Student Status Management</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Toggle Student Status Active to Inactive</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Verify that toggling student status to Inactive automatically sets Dropout Date to today.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 is Active with no Dropout Date.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Inactive</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>1. Open ST001 profile and click Edit;
 2. Change status to Inactive;
@@ -3048,70 +3053,74 @@
 4. Open ST001 profile details</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Student status is saved as Inactive. The Dropout Date is automatically set to today's date (e.g. 2026-07-17) without manual input.</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Student status is saved as Inactive. The Dropout Date is automatically set to today's date (e.g. 2026-07-17) without manual input.</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-026</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>M01-F08</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Student Status Management</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Toggle Student Status Inactive to Active</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Verify that toggling student status to Active automatically clears Dropout Date.</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 is Inactive with Dropout Date '2026-07-17'.</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Active</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>1. Open ST001 profile and click Edit;
 2. Change status to Active;
@@ -3119,211 +3128,148 @@
 4. Open ST001 profile details</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Student status is saved as Active. The Dropout Date field is automatically cleared and is now blank.</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Student status is saved as Active. The Dropout Date field is automatically cleared and is now blank.</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="75" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-027</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="25" ht="75" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Search Student by Name Real-time</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>Verify that searching student list by name filters records dynamically in real-time as the user types.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student list contains 'Nguyen Van A' and 'Tran Thi B'.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>SearchQuery=Nguyen</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>1. Navigate to student list;
 2. Place cursor in Search box and type 'Nguyen';
 3. Observe student list</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>The student list filters dynamically while typing. Tran Thi B is hidden, and Nguyen Van A remains visible. No page reload occurs.</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>The student list filters dynamically while typing. Tran Thi B is hidden, and Nguyen Van A remains visible. No page reload occurs.</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-09</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-028</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+    <row r="26" ht="105" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Filter Students by Observation Rating</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Verify that staff can filter students by their observation rating.</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Students exist with different observation ratings.</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>RatingFilter=Good</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>1. Open student list;
-2. Click the Observation Rating filter dropdown;
-3. Choose Good;
-4. Observe the filtered list</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>The student list is filtered to display only students with a "Good" rating. Other students are hidden.</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F09, Scenario: BS-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="105" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-029</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>M01-F09</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Search &amp; Filter</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify Student List Default Pagination</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Verify that the student list displays exactly 10 students per page by default.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. There are 12 students in the selected batch.</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>Batch PNV26A has 12 students.</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to the student list of batch PNV26A;
 2. Count the number of students displayed on the first page;
@@ -3331,769 +3277,589 @@
 4. Click Next Page</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>Page 1 displays exactly 10 students. Pagination controls are visible. Clicking Next Page shows the remaining 2 students on page 2.</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Page 1 displays exactly 10 students. Pagination controls are visible. Clicking Next Page shows the remaining 2 students on page 2.</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-10</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="75" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-030</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>M01-F10</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Dashboard Overview</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Verify Dashboard Displays Correct Initial Stats and Charts</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Verify that the dashboard screen accurately loads and displays all student and batch metrics.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Staff user is logged in. System has 2 batches (1 Active, 1 Archived) and 5 students (4 Active, 1 Inactive).</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>1. Navigate to the Dashboard Overview page;
 2. Observe the statistics cards and charts</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>The dashboard displays: Total Batches = 2, Active Batches = 1, Total Students = 5, Active Students = 4, Inactive Students = 1. Charts (Gender, Ethnicity, Status) load successfully.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>The dashboard displays: Total Batches = 2, Active Batches = 1, Total Students = 5, Active Students = 4, Inactive Students = 1. Charts (Gender, Ethnicity, Status) load successfully.</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-031</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>M01-F10</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Dashboard Overview</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Verify Dashboard Stats Auto-refresh after Data Changes</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Verify that dashboard statistics and charts refresh automatically when data changes.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Dashboard shows Active Students = 4.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewStatus=Inactive</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to student list and edit ST001 to change status from Active to Inactive;
 2. Click Save;
 3. Immediately return to the Dashboard</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>The dashboard values update without manual page reload: Active Students displays 3, Inactive Students displays 2, and charts adjust accordingly.</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>The dashboard values update without manual page reload: Active Students displays 3, Inactive Students displays 2, and charts adjust accordingly.</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-032</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-028</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Staff User Access to Student Management</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>Verify that staff users with a valid @passerellesnumeriques.org email domain are granted access to Batch &amp; Student Management.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>User is authenticated with email staff@passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Email=staff@passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account staff@passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>The user is redirected to the Staff Portal. Full management options (Create Batch, Add Student, Edit, CSV Import) are visible and accessible.</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>The user is redirected to the Staff Portal. Full management options (Create Batch, Add Student, Edit, CSV Import) are visible and accessible.</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-033</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Student User Access to Student Management Denied</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Verify that students with a @student.passerellesnumeriques.org email are denied management access.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>User is authenticated with email student01@student.passerellesnumeriques.org.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Email=student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account student01@student.passerellesnumeriques.org</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>The user is redirected to the Student Portal. Management buttons and options are hidden. Direct URL routing to staff pages displays "Access Denied".</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>The user is redirected to the Student Portal. Management buttons and options are hidden. Direct URL routing to staff pages displays "Access Denied".</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-018</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-030</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>CSV Student Import Upsert</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Verify that bulk student import via CSV updates existing profiles and creates new profiles (Upsert behavior).</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in. Student ST001 already exists; batch PNV26A exists.</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>CSV row: ST001,Nguyen Van A Updated,2006-05-15,Male,nguyenvana.new@student.passerellesnumeriques.org,AssociatedBatch=PNV26A and ST003,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org,AssociatedBatch=PNV26A</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page;
-2. Upload CSV containing update row for ST001 and new row for ST003;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>Import completes successfully. Message displays "Import successful. 1 student updated, 1 student created.". ST001 displays new name and ST003 appears in list.</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-019</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>CSV Student Import Rejects Duplicate Student Codes</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Verify that student bulk import via CSV rejects imports with duplicate student codes within the file.</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>CSV containing two rows with student code ST004</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page;
-2. Upload CSV with duplicate ST004;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>The system rejects the entire CSV file. Error message appears: "Duplicate student code: ST004.". No records are imported.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Scenario: BS-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-034</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>M01-SEC</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Access Control &amp; Security</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Unknown Email Domain Access Denied</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>Verify that users with non-permitted email domains are completely blocked from accessing the system.</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>User is authenticated with email testuser@gmail.com.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>Email=testuser@gmail.com</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>1. Enter the application URL;
 2. Sign in via Google OAuth with account testuser@gmail.com;
 3. Observe the system response</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Login fails or the screen displays an "Access Denied" message. The user is not redirected to either the Staff or Student Portal.</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Login failed, or the screen displays a notification stating that this page cannot be accessed.</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Login failed, or the screen displays a notification stating that this page cannot be accessed.</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Authorization</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="135" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-035</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>M01-F04</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Single Student Creation</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Create Student Fails due to Missing Associated Batch</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Verify that manually creating a student requires selecting an Associated Batch.</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>M01-F05</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Bulk Student Import</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>CSV Student Import Fails due to Blank Name</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Verify that bulk import via CSV blocks saving if student name is empty.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>StudentCode=ST099; StudentName=Nguyen Van Test; AssociatedBatch=Empty</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>1. Open Batch Management;
-2. Click Add Student;
-3. Enter Student Code 'ST099' and Name 'Nguyen Van Test';
-4. Leave Associated Batch selection empty;
-5. Click Save</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>The system blocks saving and displays a validation error "Associated Batch is required". The batch dropdown is highlighted in red.</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F04, Validation Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="75" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-036</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>CSV Student Import Fails due to Blank Name</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>Verify that bulk import via CSV blocks saving if student name is empty.</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>Staff user is logged in.</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>CSV contains row: ST006,,2006-08-20,Male,student06@student.passerellesnumeriques.org (blank name)</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>1. Go to CSV Import page;
 2. Upload the CSV file with blank name;
 3. Click Import</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>The system rejects the entire CSV file with error message "Student Name is required". No records are updated in database.</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>The system rejects the entire CSV file with error message "Student Name is required". No records are updated in database.</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Validation Rules</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="75" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>TC-M01-032</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>M01-F09</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Search &amp; Filter</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Search Student Case Insensitivity</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>Verify that student search filters correctly regardless of character casing.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Staff user is logged in. Batch PNV26A contains student 'Nguyen Van A'.</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>SearchQuery=nguyen van a</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>1. Open student list;
 2. Enter 'nguyen van a' (all lowercase) in the search box;
 3. Verify matching result</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>The student list filters and displays 'Nguyen Van A', proving search is case-insensitive.</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>The student list filters and displays 'Nguyen Van A', proving search is case-insensitive.</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Search &amp; Filter</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>TC-M01-038</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-M01-033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Module 01</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>M01-F06</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Student Editing</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Edit Student Email to Invalid Format Blocked</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Verify that editing a student's email to an invalid format is blocked.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Staff user is logged in. Student ST001 exists.</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>StudentCode=ST001; NewEmail=nguyenvana_invalid_email</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>1. Open student list;
 2. Select ST001 and click Edit;
@@ -4101,105 +3867,39 @@
 4. Click Save</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>The system blocks saving and displays a validation error message requiring a valid email format. The email field is highlighted in red.</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>The system successfully updated the email address, even though the format was incorrect.</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F06, Validation Rules</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="75" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TC-M01-039</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Module 01</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>M01-F05</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Bulk Student Import</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>CSV Student Import Blocked due to Duplicate Student Code in Another Batch</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Verify that CSV student import rejects student codes that are already in use in other batches.</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Student ST001 exists in batch PNV26A. Batch PNV26B has no students.</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>CSV file for batch PNV26B containing row: ST001,Le Van C,2006-08-20,Male,levanc.st26@student.passerellesnumeriques.org</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>1. Go to CSV Import page for batch PNV26B;
-2. Upload CSV containing student ST001;
-3. Click Import</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>The system rejects the import and displays error message "Duplicate student code: ST001.". No students are added.</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M01-F05, Student Code Uniqueness</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N40"/>
+  <autoFilter ref="A1:N34"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="L2:L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="M2:M134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module01_test_cases.xlsx
+++ b/Tests/excel/module01_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module01" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module01'!$A$1:$N$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module01'!$A$1:$O$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1003,15 +1003,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A9, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1031,15 +1031,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A10, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1059,15 +1059,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A11, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A12, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1115,15 +1115,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A13, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1143,15 +1143,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A14, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A15, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1199,15 +1199,15 @@
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A16, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1227,15 +1227,15 @@
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A17, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1255,15 +1255,15 @@
         </is>
       </c>
       <c r="C18" s="30">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D18" s="31">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A18, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F18" s="33">
@@ -1283,15 +1283,15 @@
         </is>
       </c>
       <c r="C19" s="24">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "High")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$N$2:$N$34, "High")</f>
         <v/>
       </c>
       <c r="D19" s="25">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "Medium")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$N$2:$N$34, "Medium")</f>
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$M$2:$M$34, "Low")</f>
+        <f>COUNTIFS('Module01'!$C$2:$C$34, A19, 'Module01'!$N$2:$N$34, "Low")</f>
         <v/>
       </c>
       <c r="F19" s="27">
@@ -1338,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1353,8 +1353,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1420,10 +1421,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1494,12 +1500,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1569,12 +1576,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1644,12 +1652,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1719,12 +1728,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1794,12 +1804,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1869,12 +1880,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -1944,12 +1956,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F01, Scenario: BS-01</t>
         </is>
@@ -2019,12 +2032,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F02, Scenario: BS-02</t>
         </is>
@@ -2094,12 +2108,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F02, Scenario: BS-02</t>
         </is>
@@ -2169,12 +2184,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F02, Scenario: BS-02</t>
         </is>
@@ -2243,12 +2259,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F03, Scenario: BS-03</t>
         </is>
@@ -2318,12 +2335,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F03, Scenario: BS-03</t>
         </is>
@@ -2392,12 +2410,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F03, Scenario: BS-03</t>
         </is>
@@ -2470,12 +2489,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F04, Scenario: BS-04</t>
         </is>
@@ -2546,12 +2566,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F04, Scenario: BS-04</t>
         </is>
@@ -2621,12 +2642,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F04, Scenario: BS-04</t>
         </is>
@@ -2695,12 +2717,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Scenario: BS-05</t>
         </is>
@@ -2769,12 +2792,13 @@
           <t>Failed</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Scenario: BS-05</t>
         </is>
@@ -2843,12 +2867,13 @@
           <t>Failed</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Scenario: BS-05</t>
         </is>
@@ -2918,12 +2943,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F06, Scenario: BS-06</t>
         </is>
@@ -2993,12 +3019,13 @@
           <t>Failed</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F07, Scenario: BS-07</t>
         </is>
@@ -3068,12 +3095,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
@@ -3143,12 +3171,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F08, Scenario: BS-08</t>
         </is>
@@ -3217,12 +3246,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-09</t>
         </is>
@@ -3292,12 +3322,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Scenario: BS-10</t>
         </is>
@@ -3365,12 +3396,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
@@ -3439,12 +3471,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F10, Scenario: BS-11</t>
         </is>
@@ -3512,12 +3545,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
@@ -3585,12 +3619,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Scenario: BS-12</t>
         </is>
@@ -3659,12 +3694,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: General Business Rules, Authorization</t>
         </is>
@@ -3733,12 +3769,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F05, Validation Rules</t>
         </is>
@@ -3807,12 +3844,13 @@
           <t>Passed</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F09, Search &amp; Filter</t>
         </is>
@@ -3882,24 +3920,25 @@
           <t>Failed</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M01-F06, Validation Rules</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N34"/>
+  <autoFilter ref="A1:O34"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
